--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484308_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484308_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9183</v>
+        <v>3.9727</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0892</v>
+        <v>1.6297</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8291</v>
+        <v>2.3431</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2343</v>
+        <v>2.4131</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7071</v>
+        <v>-0.4057</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4728</v>
+        <v>2.8188</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1296</v>
+        <v>1.9584</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2755</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1459</v>
+        <v>1.8752</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1047</v>
+        <v>0.4547</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5684</v>
+        <v>-0.4889</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6731</v>
+        <v>0.9435</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3208</v>
+        <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5668</v>
+        <v>-0.6672</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4487</v>
+        <v>-0.1334</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1181</v>
+        <v>-0.5339</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0549</v>
+        <v>0.6642</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6596</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7145</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.066</v>
+        <v>3.0777</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8319</v>
+        <v>1.9415</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2341</v>
+        <v>1.1363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4131</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4057</v>
+        <v>-1.7803</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8188</v>
+        <v>1.1457</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9584</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08309999999999999</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8752</v>
+        <v>0.7422</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4547</v>
+        <v>-0.7091</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4889</v>
+        <v>-1.1125</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9435</v>
+        <v>0.4035</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>3.1255</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5739</v>
+        <v>-1.0104</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0689</v>
+        <v>-0.6168</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6428</v>
+        <v>-0.3936</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6642</v>
+        <v>2.7693</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.6559</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4319</v>
+        <v>2.7421</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8404</v>
+        <v>1.1386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5915</v>
+        <v>1.6035</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6346000000000001</v>
+        <v>1.2343</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7803</v>
+        <v>1.7071</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1457</v>
+        <v>-0.4728</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07439999999999999</v>
+        <v>1.1296</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6677999999999999</v>
+        <v>2.2755</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7422</v>
+        <v>-1.1459</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7091</v>
+        <v>0.1047</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1125</v>
+        <v>-0.5684</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4035</v>
+        <v>0.6731</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1255</v>
+        <v>3.3208</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6562</v>
+        <v>0.3906</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7179</v>
+        <v>-0.5019</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9383</v>
+        <v>0.8925</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7693</v>
+        <v>-0.0549</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6559</v>
+        <v>2.6596</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8865</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7015</v>
+        <v>2.5011</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.574</v>
+        <v>-0.2102</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2755</v>
+        <v>2.7113</v>
       </c>
       <c r="G5" t="n">
         <v>1.4365</v>
@@ -844,13 +844,13 @@
         <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2309</v>
+        <v>-0.4313</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0289</v>
+        <v>-0.665</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.202</v>
+        <v>0.2337</v>
       </c>
       <c r="V5" t="n">
         <v>1.4959</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3288</v>
+        <v>1.5322</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9076</v>
+        <v>0.0858</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2364</v>
+        <v>1.4464</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8444</v>
+        <v>2.6135</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5421</v>
+        <v>-0.9197</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3865</v>
+        <v>3.5332</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1488</v>
+        <v>3.5825</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1599</v>
+        <v>0.4528</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3087</v>
+        <v>3.1297</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3044</v>
+        <v>-0.969</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3822</v>
+        <v>-1.3725</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0778</v>
+        <v>0.4035</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3208</v>
+        <v>2.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.004</v>
+        <v>-0.4636</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7784</v>
+        <v>-0.5034</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7745</v>
+        <v>0.0398</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6604</v>
+        <v>0.5545</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.1059</v>
+        <v>1.1089</v>
       </c>
       <c r="X6" t="n">
         <v>-0.5545</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9084</v>
+        <v>1.3969</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6914</v>
+        <v>0.853</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2171</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>2.2585</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1082</v>
+        <v>-0.6197</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2004</v>
+        <v>0.1265</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2186</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8282</v>
+        <v>0.9124</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3186</v>
+        <v>-1.8065</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1468</v>
+        <v>2.719</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6135</v>
+        <v>0.8444</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9197</v>
+        <v>-1.5421</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5332</v>
+        <v>2.3865</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5825</v>
+        <v>1.1488</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4528</v>
+        <v>-0.1599</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1297</v>
+        <v>1.3087</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.969</v>
+        <v>-0.3044</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3725</v>
+        <v>-1.3822</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4035</v>
+        <v>1.0778</v>
       </c>
       <c r="P8" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-4.1022</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.9301</v>
+        <v>3.3208</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1677</v>
+        <v>-0.4203</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6773</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2598</v>
+        <v>0.257</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5545</v>
+        <v>-1.6604</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1089</v>
+        <v>-1.1059</v>
       </c>
       <c r="X8" t="n">
         <v>-0.5545</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3785</v>
+        <v>-0.0068</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6833</v>
+        <v>-0.4205</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3048</v>
+        <v>0.4137</v>
       </c>
       <c r="G9" t="n">
         <v>1.1582</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3181</v>
+        <v>0.0536</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5447</v>
+        <v>-0.282</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2266</v>
+        <v>0.3356</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9311</v>
+        <v>-1.0612</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1244</v>
+        <v>-1.0639</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933</v>
+        <v>0.0027</v>
       </c>
       <c r="G10" t="n">
         <v>0.243</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3571</v>
+        <v>0.227</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>-0.0605</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4781</v>
+        <v>0.2875</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5545</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7759</v>
+        <v>-2.667</v>
       </c>
       <c r="E11" t="n">
         <v>-1.7506</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0254</v>
+        <v>-0.9164</v>
       </c>
       <c r="G11" t="n">
         <v>-1.081</v>
@@ -1312,13 +1312,13 @@
         <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3043</v>
+        <v>-0.1953</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0622</v>
+        <v>0.0467</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6093</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.0976</v>
+        <v>12.4001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09440000000000026</v>
+        <v>0.3969</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0032</v>
+        <v>12.0035</v>
       </c>
       <c r="G12" t="n">
         <v>10.4859</v>
@@ -1366,16 +1366,16 @@
         <v>10.6851</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6345</v>
+        <v>6.634499999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.0504</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1992</v>
+        <v>-0.1991999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.912900000000001</v>
+        <v>-4.9129</v>
       </c>
       <c r="O12" t="n">
         <v>4.7138</v>
@@ -1390,10 +1390,10 @@
         <v>18.5574</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.4394</v>
+        <v>-3.1366</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.731000000000001</v>
+        <v>-4.428599999999999</v>
       </c>
       <c r="U12" t="n">
         <v>1.2918</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0182</v>
+        <v>2.2688</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6955</v>
+        <v>3.1793</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6773</v>
+        <v>-0.9105</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4906</v>
+        <v>1.4215</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3323</v>
+        <v>0.7186</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8229</v>
+        <v>0.7029</v>
       </c>
       <c r="J13" t="n">
-        <v>0.413</v>
+        <v>2.3252</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9657</v>
+        <v>1.352</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5527</v>
+        <v>0.9732</v>
       </c>
       <c r="M13" t="n">
         <v>-0.9036</v>
@@ -1459,37 +1459,37 @@
         <v>-0.2702</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6336</v>
+        <v>0.5971</v>
       </c>
       <c r="T13" t="n">
-        <v>1.728</v>
+        <v>0.1983</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9055</v>
+        <v>0.3988</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8828</v>
+        <v>0.0549</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5545</v>
+        <v>1.8279</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4373</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8875</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1793</v>
+        <v>1.5832</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2918</v>
+        <v>-1.0313</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4215</v>
+        <v>-0.4906</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7186</v>
+        <v>0.3323</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7029</v>
+        <v>-0.8229</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3252</v>
+        <v>0.413</v>
       </c>
       <c r="K14" t="n">
-        <v>1.352</v>
+        <v>0.9657</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9732</v>
+        <v>-0.5527</v>
       </c>
       <c r="M14" t="n">
         <v>-0.9036</v>
@@ -1537,37 +1537,37 @@
         <v>-0.2702</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2158</v>
+        <v>1.1673</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1983</v>
+        <v>0.6158</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0175</v>
+        <v>0.5515</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0549</v>
+        <v>-1.8828</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7731</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.058</v>
+        <v>0.0658</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4752</v>
+        <v>-0.9691</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5332</v>
+        <v>1.0349</v>
       </c>
       <c r="G15" t="n">
-        <v>0.904</v>
+        <v>-1.8909</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6866</v>
+        <v>-2.0658</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7827</v>
+        <v>0.1749</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4169</v>
+        <v>-1.2668</v>
       </c>
       <c r="K15" t="n">
-        <v>2.255</v>
+        <v>-1.3073</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5129</v>
+        <v>-0.6241</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5684</v>
+        <v>-0.7585</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9445</v>
+        <v>0.1344</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.1022</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3028</v>
+        <v>0.9334</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9329</v>
+        <v>0.0558</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3699</v>
+        <v>0.8776</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6259</v>
+        <v>-0.0574</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4635</v>
+        <v>-0.1342</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0893</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8909</v>
+        <v>-0.0946</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0658</v>
+        <v>0.1348</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1749</v>
+        <v>-0.2294</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2668</v>
+        <v>0.0405</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6241</v>
+        <v>-0.135</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7585</v>
+        <v>0.1348</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1344</v>
+        <v>-0.2698</v>
       </c>
       <c r="P16" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4935</v>
+        <v>0.2325</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5614</v>
+        <v>0.0207</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.2118</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2052</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3364</v>
+        <v>-1.2841</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1313</v>
+        <v>0.7161</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0946</v>
+        <v>0.904</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1348</v>
+        <v>1.6866</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2294</v>
+        <v>-0.7827</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0405</v>
+        <v>2.4169</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.255</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>0.1619</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.135</v>
+        <v>-1.5129</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1348</v>
+        <v>-0.5684</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2698</v>
+        <v>-0.9445</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-4.1022</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0847</v>
+        <v>0.6768</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1816</v>
+        <v>0.124</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2663</v>
+        <v>0.5528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. EXPOSITO FORTUNY</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.925</v>
+        <v>-0.8728</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6488</v>
+        <v>-1.6757</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7238</v>
+        <v>0.8028</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3979</v>
+        <v>-0.1026</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2244</v>
+        <v>0.626</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1735</v>
+        <v>-0.7286</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1645</v>
+        <v>0.6565</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5308</v>
+        <v>1.2497</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2334</v>
+        <v>-0.7591</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6935</v>
+        <v>-0.6237</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5399</v>
+        <v>-0.1354</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1365</v>
+        <v>0.4334</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.2337</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5898</v>
+        <v>0.6671</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0.8317</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>G. EXPOSITO FORTUNY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9545</v>
+        <v>-0.8862</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6757</v>
+        <v>-1.4466</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7211</v>
+        <v>0.5604</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1026</v>
+        <v>-2.3979</v>
       </c>
       <c r="H19" t="n">
-        <v>0.626</v>
+        <v>-1.2244</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7286</v>
+        <v>-1.1735</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6565</v>
+        <v>-1.1645</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2497</v>
+        <v>-0.5308</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7591</v>
+        <v>-1.2334</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6237</v>
+        <v>-0.6935</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1354</v>
+        <v>-0.5399</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3517</v>
+        <v>-0.0977</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2337</v>
+        <v>-0.524</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5854</v>
+        <v>0.4264</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8317</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9315</v>
+        <v>-0.9163</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4865</v>
+        <v>-0.8798</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.445</v>
+        <v>-0.0365</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2467</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4774</v>
+        <v>-0.4622</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2105</v>
+        <v>-0.6038</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2669</v>
+        <v>0.1416</v>
       </c>
       <c r="V20" t="n">
         <v>1.5507</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9632</v>
+        <v>-1.6865</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1378</v>
+        <v>-3.2064</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8254</v>
+        <v>1.5199</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0853</v>
+        <v>-1.1983</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2203</v>
+        <v>0.7703</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.135</v>
+        <v>-1.9686</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0205</v>
+        <v>0.1796</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>1.4735</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.2939</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0648</v>
+        <v>-1.3779</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1998</v>
+        <v>-0.7032</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.135</v>
+        <v>-0.6747</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0484</v>
+        <v>-0.2538</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1816</v>
+        <v>-0.2606</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1331</v>
+        <v>0.0068</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8028</v>
+        <v>-1.8542</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9142</v>
+        <v>-1.1378</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1114</v>
+        <v>-0.7164</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1983</v>
+        <v>0.0853</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7703</v>
+        <v>0.2203</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9686</v>
+        <v>-0.135</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1796</v>
+        <v>0.0205</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4735</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2939</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3779</v>
+        <v>0.0648</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7032</v>
+        <v>0.1998</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>-0.135</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3701</v>
+        <v>0.0605</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9684</v>
+        <v>-0.1816</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4017</v>
+        <v>0.2421</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3283</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.3283</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0152</v>
+        <v>-2.8324</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6804</v>
+        <v>-1.5793</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3347</v>
+        <v>-1.253</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0758</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4435</v>
+        <v>-0.2607</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6252</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2828</v>
+        <v>0.3645</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4959</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8899</v>
+        <v>-5.3104</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0596</v>
+        <v>-4.4529</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8303</v>
+        <v>-0.8575</v>
       </c>
       <c r="G24" t="n">
         <v>-5.3993</v>
@@ -2326,13 +2326,13 @@
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1668</v>
+        <v>0.4127</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4842</v>
+        <v>0.1225</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3174</v>
+        <v>0.2902</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4959</v>
@@ -2362,10 +2362,10 @@
         <v>-12.0977</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.0033</v>
+        <v>-12.0034</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.09440000000000071</v>
+        <v>-0.09430000000000038</v>
       </c>
       <c r="G25" t="n">
         <v>-10.4859</v>
@@ -2374,7 +2374,7 @@
         <v>-1.7218</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.7644</v>
+        <v>-8.764399999999998</v>
       </c>
       <c r="J25" t="n">
         <v>0.1991999999999994</v>
@@ -2389,10 +2389,10 @@
         <v>-10.685</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.6345</v>
+        <v>-6.634499999999998</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.0504</v>
+        <v>-4.050400000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-4.8835</v>
@@ -2404,13 +2404,13 @@
         <v>13.674</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4394</v>
+        <v>3.4393</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.292</v>
+        <v>-1.2918</v>
       </c>
       <c r="U25" t="n">
-        <v>4.7311</v>
+        <v>4.731199999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1676000000000002</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484308_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484308_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5011</v>
+        <v>2.7419</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2102</v>
+        <v>2.7419</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7113</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4365</v>
+        <v>2.7419</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8386</v>
+        <v>0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4021</v>
+        <v>1.821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9124</v>
+        <v>2.7419</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3139</v>
+        <v>0.921</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4015</v>
+        <v>1.821</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5241</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5247000000000001</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4313</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.665</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2337</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +902,72 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5322</v>
+        <v>2.5011</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0858</v>
+        <v>-0.2102</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4464</v>
+        <v>2.7113</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6135</v>
+        <v>1.4365</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9197</v>
+        <v>2.8386</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5332</v>
+        <v>-1.4021</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5825</v>
+        <v>0.9124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4528</v>
+        <v>2.3139</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1297</v>
+        <v>-1.4015</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.969</v>
+        <v>0.5241</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3725</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4035</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1022</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9301</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4636</v>
+        <v>-0.4313</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5034</v>
+        <v>-0.665</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0398</v>
+        <v>0.2337</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5545</v>
+        <v>1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1089</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9124</v>
+        <v>0.9183</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8065</v>
+        <v>-0.5282</v>
       </c>
       <c r="F8" t="n">
-        <v>2.719</v>
+        <v>1.4464</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8444</v>
+        <v>1.9995</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5421</v>
+        <v>-1.5337</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3865</v>
+        <v>3.5332</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1488</v>
+        <v>2.9685</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1599</v>
+        <v>-0.1612</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3087</v>
+        <v>3.1297</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3044</v>
+        <v>-0.969</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3822</v>
+        <v>-1.3725</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0778</v>
+        <v>0.4035</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3208</v>
+        <v>2.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4203</v>
+        <v>-0.4636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6773</v>
+        <v>-0.5034</v>
       </c>
       <c r="U8" t="n">
-        <v>0.257</v>
+        <v>0.0398</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6604</v>
+        <v>0.5545</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.1059</v>
+        <v>1.1089</v>
       </c>
       <c r="X8" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0068</v>
+        <v>0.614</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4205</v>
+        <v>0.614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4137</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1582</v>
+        <v>0.614</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4032</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>0.755</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7572</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3201</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0536</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.282</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3356</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0612</v>
+        <v>-0.0068</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0639</v>
+        <v>-0.4205</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0027</v>
+        <v>0.4137</v>
       </c>
       <c r="G10" t="n">
-        <v>0.243</v>
+        <v>1.1582</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2696</v>
+        <v>0.4032</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0266</v>
+        <v>0.755</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0266</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.7572</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0266</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2696</v>
+        <v>0.3201</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2696</v>
+        <v>-0.354</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.6741</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.227</v>
+        <v>0.0536</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0605</v>
+        <v>-0.282</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2875</v>
+        <v>0.3356</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.667</v>
+        <v>-1.0612</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7506</v>
+        <v>-1.0639</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9164</v>
+        <v>0.0027</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.081</v>
+        <v>0.243</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4876</v>
+        <v>0.2696</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5934</v>
+        <v>-0.0266</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.0266</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.0266</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5492</v>
+        <v>0.2696</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.549</v>
+        <v>0.2696</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1953</v>
+        <v>0.227</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2421</v>
+        <v>-0.0605</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0467</v>
+        <v>0.2875</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.4001</v>
+        <v>-1.8295</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3969</v>
+        <v>-4.5484</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0035</v>
+        <v>2.719</v>
       </c>
       <c r="G12" t="n">
-        <v>10.4859</v>
+        <v>-1.8975</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7216</v>
+        <v>-2.4631</v>
       </c>
       <c r="I12" t="n">
-        <v>8.764299999999999</v>
+        <v>0.5655</v>
       </c>
       <c r="J12" t="n">
-        <v>10.6851</v>
+        <v>-1.5931</v>
       </c>
       <c r="K12" t="n">
-        <v>6.634499999999999</v>
+        <v>-1.0809</v>
       </c>
       <c r="L12" t="n">
-        <v>4.0504</v>
+        <v>-0.5122</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1991999999999999</v>
+        <v>-0.3044</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.9129</v>
+        <v>-1.3822</v>
       </c>
       <c r="O12" t="n">
-        <v>4.7138</v>
+        <v>1.0778</v>
       </c>
       <c r="P12" t="n">
-        <v>4.883500000000001</v>
+        <v>2.1488</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.674</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>18.5574</v>
+        <v>3.3208</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.1366</v>
+        <v>-0.4203</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.428599999999999</v>
+        <v>-0.6773</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2918</v>
+        <v>0.257</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1676000000000004</v>
+        <v>-1.6604</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8144</v>
+        <v>-1.1059</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.6468</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2688</v>
+        <v>-2.667</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1793</v>
+        <v>-1.7506</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9105</v>
+        <v>-0.9164</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4215</v>
+        <v>-1.081</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7186</v>
+        <v>-0.4876</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7029</v>
+        <v>-0.5934</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3252</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.352</v>
+        <v>0.0614</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9732</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9036</v>
+        <v>-0.5492</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6334</v>
+        <v>-0.549</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2702</v>
+        <v>-0.0002</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.1953</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-1.1721</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3674</v>
-      </c>
       <c r="S13" t="n">
-        <v>0.5971</v>
+        <v>-0.1953</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1983</v>
+        <v>-0.2421</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3988</v>
+        <v>0.0467</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0549</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7731</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5518999999999999</v>
+        <v>12.4002</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5832</v>
+        <v>0.3968999999999991</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0313</v>
+        <v>12.0035</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4906</v>
+        <v>10.4859</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3323</v>
+        <v>1.721599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8229</v>
+        <v>8.7643</v>
       </c>
       <c r="J14" t="n">
-        <v>0.413</v>
+        <v>10.6851</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9657</v>
+        <v>6.634500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5527</v>
+        <v>4.0505</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9036</v>
+        <v>-0.1991999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6334</v>
+        <v>-4.9129</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2702</v>
+        <v>4.7138</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7581</v>
+        <v>4.8835</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-13.674</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>18.5574</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1673</v>
+        <v>-3.1366</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6158</v>
+        <v>-4.428599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5515</v>
+        <v>1.2918</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8828</v>
+        <v>0.1676</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>7.814400000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4373</v>
-      </c>
+        <v>-7.6468</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0658</v>
+        <v>2.2688</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9691</v>
+        <v>3.1793</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0349</v>
+        <v>-0.9105</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8909</v>
+        <v>1.4215</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.0658</v>
+        <v>0.7186</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1749</v>
+        <v>0.7029</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2668</v>
+        <v>2.3252</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3073</v>
+        <v>1.352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>0.9732</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6241</v>
+        <v>-0.9036</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7585</v>
+        <v>-0.6334</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>-0.2702</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9334</v>
+        <v>0.5971</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0558</v>
+        <v>0.1983</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8776</v>
+        <v>0.3988</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>0.0549</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0574</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1342</v>
+        <v>1.5832</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07679999999999999</v>
+        <v>-1.0313</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0946</v>
+        <v>-0.4906</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1348</v>
+        <v>0.3323</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2294</v>
+        <v>-0.8229</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0405</v>
+        <v>0.413</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.9657</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>-0.5527</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.135</v>
+        <v>-0.9036</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1348</v>
+        <v>-0.6334</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2698</v>
+        <v>-0.2702</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2325</v>
+        <v>1.1673</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0207</v>
+        <v>0.6158</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2118</v>
+        <v>0.5515</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.0658</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2841</v>
+        <v>-0.9691</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7161</v>
+        <v>1.0349</v>
       </c>
       <c r="G17" t="n">
-        <v>0.904</v>
+        <v>-1.8909</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6866</v>
+        <v>-2.0658</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7827</v>
+        <v>0.1749</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4169</v>
+        <v>-1.2668</v>
       </c>
       <c r="K17" t="n">
-        <v>2.255</v>
+        <v>-1.3073</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5129</v>
+        <v>-0.6241</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5684</v>
+        <v>-0.7585</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9445</v>
+        <v>0.1344</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1022</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6768</v>
+        <v>0.9334</v>
       </c>
       <c r="T17" t="n">
-        <v>0.124</v>
+        <v>0.0558</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5528</v>
+        <v>0.8776</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8728</v>
+        <v>-0.0574</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6757</v>
+        <v>-0.1342</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8028</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1026</v>
+        <v>-0.0946</v>
       </c>
       <c r="H18" t="n">
-        <v>0.626</v>
+        <v>0.1348</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7286</v>
+        <v>-0.2294</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6565</v>
+        <v>0.0405</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2497</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7591</v>
+        <v>-0.135</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6237</v>
+        <v>0.1348</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1354</v>
+        <v>-0.2698</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4334</v>
+        <v>0.2325</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2337</v>
+        <v>0.0207</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6671</v>
+        <v>0.2118</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. EXPOSITO FORTUNY</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8862</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4466</v>
+        <v>-1.2841</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5604</v>
+        <v>0.7161</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3979</v>
+        <v>0.904</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2244</v>
+        <v>1.6866</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1735</v>
+        <v>-0.7827</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1645</v>
+        <v>2.4169</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5308</v>
+        <v>2.255</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.1619</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2334</v>
+        <v>-1.5129</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6935</v>
+        <v>-0.5684</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5399</v>
+        <v>-0.9445</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0977</v>
+        <v>0.6768</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.524</v>
+        <v>0.124</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4264</v>
+        <v>0.5528</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9163</v>
+        <v>-0.8728</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8798</v>
+        <v>-1.6757</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0365</v>
+        <v>0.8028</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2467</v>
+        <v>-0.1026</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2239</v>
+        <v>0.626</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4706</v>
+        <v>-0.7286</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1312</v>
+        <v>0.6565</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3315</v>
+        <v>1.2497</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2004</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3779</v>
+        <v>-0.7591</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1077</v>
+        <v>-0.6237</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2702</v>
+        <v>-0.1354</v>
       </c>
       <c r="P20" t="n">
         <v>-1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4622</v>
+        <v>0.4334</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6038</v>
+        <v>-0.2337</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1416</v>
+        <v>0.6671</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5507</v>
+        <v>0.5545</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7182</v>
+        <v>0.8317</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1675</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. EXPOSITO FORTUNY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6865</v>
+        <v>-0.8862</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2064</v>
+        <v>-1.4466</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5199</v>
+        <v>0.5604</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1983</v>
+        <v>-2.3979</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7703</v>
+        <v>-1.2244</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9686</v>
+        <v>-1.1735</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1796</v>
+        <v>-1.1645</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4735</v>
+        <v>-0.5308</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2939</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3779</v>
+        <v>-1.2334</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7032</v>
+        <v>-0.6935</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6747</v>
+        <v>-0.5399</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2538</v>
+        <v>-0.0977</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2606</v>
+        <v>-0.524</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0068</v>
+        <v>0.4264</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3283</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8542</v>
+        <v>-0.9163</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1378</v>
+        <v>-0.8798</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7164</v>
+        <v>-0.0365</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0853</v>
+        <v>-0.2467</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2203</v>
+        <v>0.2239</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.135</v>
+        <v>-0.4706</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0205</v>
+        <v>1.1312</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0205</v>
+        <v>1.3315</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.2004</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0648</v>
+        <v>-1.3779</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1998</v>
+        <v>-1.1077</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.135</v>
+        <v>-0.2702</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0605</v>
+        <v>-0.4622</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1816</v>
+        <v>-0.6038</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2421</v>
+        <v>0.1416</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>1.5507</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7182</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-0.1675</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8324</v>
+        <v>-1.6865</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5793</v>
+        <v>-3.2064</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.253</v>
+        <v>1.5199</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0758</v>
+        <v>-1.1983</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1722</v>
+        <v>0.7703</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.9686</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0225</v>
+        <v>0.1796</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6562</v>
+        <v>1.4735</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2939</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0984</v>
+        <v>-1.3779</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8283</v>
+        <v>-0.7032</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.27</v>
+        <v>-0.6747</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2607</v>
+        <v>-0.2538</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6252</v>
+        <v>-0.2606</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3645</v>
+        <v>0.0068</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4959</v>
+        <v>1.3283</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3104</v>
+        <v>-1.8542</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4529</v>
+        <v>-1.1378</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8575</v>
+        <v>-0.7164</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.3993</v>
+        <v>0.0853</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.9722</v>
+        <v>0.2203</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.4272</v>
+        <v>-0.135</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.5754</v>
+        <v>0.0205</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.5531</v>
+        <v>0.0205</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0223</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8239</v>
+        <v>0.0648</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.419</v>
+        <v>0.1998</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4049</v>
+        <v>-0.135</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4127</v>
+        <v>0.0605</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1225</v>
+        <v>-0.1816</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2902</v>
+        <v>0.2421</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-2.8324</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.5793</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.253</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.0758</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.1722</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.9036999999999999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.0984</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.8283</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.2607</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.6252</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J. AURO GARRIGA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.3104</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.4529</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.8575</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-5.3993</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.9722</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.4272</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-4.5754</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2.5531</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.8239</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.419</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484308_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-12.0977</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>-12.0034</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>-0.09430000000000038</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>-10.4859</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>-1.7218</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>-8.764399999999998</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J27" t="n">
         <v>0.1991999999999994</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>4.9129</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L27" t="n">
         <v>-4.7136</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>-10.685</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-6.634499999999998</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>-4.050400000000001</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>-4.8835</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-18.5575</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>13.674</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>3.4393</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>-1.2918</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>4.731199999999999</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>-0.1676000000000002</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>7.6467</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-7.814399999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
